--- a/BOM/Setsco_List/SetscoList.xlsx
+++ b/BOM/Setsco_List/SetscoList.xlsx
@@ -1,17 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="7" rupBuild="9303"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jordan/Alitec/docker/odoo18/repo/lingjack-import-script/BOM/Setsco_List/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{675ADE8C-26A3-8E43-8B02-89EE94FBCF66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-15" yWindow="-15" windowWidth="28830" windowHeight="7305" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Office" sheetId="3" r:id="rId1"/>
     <sheet name="Production" sheetId="5" r:id="rId2"/>
     <sheet name="Warehouse" sheetId="6" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="145621"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -259,8 +265,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="6">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -466,7 +472,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -474,12 +480,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -513,7 +514,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="1" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -521,7 +522,7 @@
     <xf numFmtId="1" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="3" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="3" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -891,22 +892,22 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G66"/>
-  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="6" max="6" width="17.109375" customWidth="1"/>
-    <col min="7" max="7" width="40.44140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.1640625" customWidth="1"/>
+    <col min="7" max="7" width="40.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="15.75">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -929,720 +930,720 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="15.95">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" s="2"/>
-      <c r="B2" s="6">
+      <c r="B2" s="5">
         <v>2028901</v>
       </c>
-      <c r="C2" s="6">
+      <c r="C2" s="5">
         <v>2029699</v>
       </c>
       <c r="G2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="15.95">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" s="2"/>
-      <c r="B3" s="7">
+      <c r="B3" s="3">
         <v>2033800</v>
       </c>
-      <c r="C3" s="7">
+      <c r="C3" s="3">
         <v>2034699</v>
       </c>
       <c r="G3" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="15.95">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" s="2"/>
-      <c r="B4" s="6">
+      <c r="B4" s="5">
         <v>2032800</v>
       </c>
-      <c r="C4" s="6">
+      <c r="C4" s="5">
         <v>2033799</v>
       </c>
       <c r="G4" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="15.95">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" s="2"/>
-      <c r="B5" s="6">
+      <c r="B5" s="5">
         <v>2031800</v>
       </c>
-      <c r="C5" s="6">
+      <c r="C5" s="5">
         <v>2032799</v>
       </c>
       <c r="G5" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="15.95">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" s="2"/>
-      <c r="B6" s="6">
+      <c r="B6" s="5">
         <v>2030800</v>
       </c>
-      <c r="C6" s="6">
+      <c r="C6" s="5">
         <v>2031799</v>
       </c>
       <c r="G6" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="15.95">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" s="2"/>
-      <c r="B7" s="6">
+      <c r="B7" s="5">
         <v>2029800</v>
       </c>
-      <c r="C7" s="6">
+      <c r="C7" s="5">
         <v>2030799</v>
       </c>
       <c r="G7" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="15.95">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" s="2"/>
-      <c r="B8" s="6">
+      <c r="B8" s="5">
         <v>2029740</v>
       </c>
-      <c r="C8" s="6">
+      <c r="C8" s="5">
         <v>2029799</v>
       </c>
       <c r="G8" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="15.95">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" s="2"/>
-      <c r="B9" s="6">
+      <c r="B9" s="5">
         <v>2029700</v>
       </c>
-      <c r="C9" s="6">
+      <c r="C9" s="5">
         <v>2029739</v>
       </c>
       <c r="G9" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="15.95">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" s="2"/>
-      <c r="B10" s="7">
+      <c r="B10" s="3">
         <v>2048440</v>
       </c>
-      <c r="C10" s="7">
+      <c r="C10" s="3">
         <v>2048799</v>
       </c>
       <c r="G10" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="15.95">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" s="2"/>
-      <c r="B11" s="7">
+      <c r="B11" s="3">
         <f>C10+1</f>
         <v>2048800</v>
       </c>
-      <c r="C11" s="7">
+      <c r="C11" s="3">
         <v>2049799</v>
       </c>
       <c r="G11" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="15.95">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" s="2"/>
-      <c r="B12" s="7">
+      <c r="B12" s="3">
         <f>C11+1</f>
         <v>2049800</v>
       </c>
-      <c r="C12" s="7">
+      <c r="C12" s="3">
         <v>2050799</v>
       </c>
       <c r="G12" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="15.95">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" s="2"/>
-      <c r="B13" s="7">
+      <c r="B13" s="3">
         <f>C12+1</f>
         <v>2050800</v>
       </c>
-      <c r="C13" s="7">
+      <c r="C13" s="3">
         <v>2051799</v>
       </c>
       <c r="G13" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="15.95">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" s="2"/>
-      <c r="B14" s="7">
+      <c r="B14" s="3">
         <f>C13+1</f>
         <v>2051800</v>
       </c>
-      <c r="C14" s="7">
+      <c r="C14" s="3">
         <v>2052799</v>
       </c>
       <c r="G14" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="15.95">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" s="2"/>
-      <c r="B15" s="7">
+      <c r="B15" s="3">
         <f>C14+1</f>
         <v>2052800</v>
       </c>
-      <c r="C15" s="7">
+      <c r="C15" s="3">
         <v>2053439</v>
       </c>
       <c r="G15" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="15.95">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" s="2"/>
-      <c r="B16" s="7">
+      <c r="B16" s="3">
         <v>2048440</v>
       </c>
-      <c r="C16" s="7">
+      <c r="C16" s="3">
         <v>2048799</v>
       </c>
       <c r="G16" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="15.95">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" s="2"/>
-      <c r="B17" s="7">
+      <c r="B17" s="3">
         <f>C16+1</f>
         <v>2048800</v>
       </c>
-      <c r="C17" s="7">
+      <c r="C17" s="3">
         <v>2049799</v>
       </c>
       <c r="G17" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="15.95">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" s="2"/>
-      <c r="B18" s="7">
+      <c r="B18" s="3">
         <f>C17+1</f>
         <v>2049800</v>
       </c>
-      <c r="C18" s="7">
+      <c r="C18" s="3">
         <v>2050799</v>
       </c>
       <c r="G18" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="15.95">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" s="2"/>
-      <c r="B19" s="7">
+      <c r="B19" s="3">
         <f>C18+1</f>
         <v>2050800</v>
       </c>
-      <c r="C19" s="7">
+      <c r="C19" s="3">
         <v>2051799</v>
       </c>
       <c r="G19" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="15.95">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" s="2"/>
-      <c r="B20" s="7">
+      <c r="B20" s="3">
         <f>C19+1</f>
         <v>2051800</v>
       </c>
-      <c r="C20" s="7">
+      <c r="C20" s="3">
         <v>2052799</v>
       </c>
       <c r="G20" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="15.95">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" s="2"/>
-      <c r="B21" s="7">
+      <c r="B21" s="3">
         <f>C20+1</f>
         <v>2052800</v>
       </c>
-      <c r="C21" s="7">
+      <c r="C21" s="3">
         <v>2053439</v>
       </c>
       <c r="G21" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="15.95">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" s="2"/>
-      <c r="B22" s="6">
+      <c r="B22" s="5">
         <v>2024666</v>
       </c>
-      <c r="C22" s="6">
+      <c r="C22" s="5">
         <v>2024699</v>
       </c>
       <c r="G22" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="15.95">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" s="2"/>
-      <c r="B23" s="6">
+      <c r="B23" s="5">
         <v>2047740</v>
       </c>
-      <c r="C23" s="6">
+      <c r="C23" s="5">
         <v>2048239</v>
       </c>
       <c r="G23" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="15.95">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24" s="2"/>
-      <c r="B24" s="6">
+      <c r="B24" s="5">
         <v>2058440</v>
       </c>
-      <c r="C24" s="7">
+      <c r="C24" s="3">
         <v>2058639</v>
       </c>
       <c r="G24" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="15.95">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" s="2"/>
-      <c r="B25" s="7">
+      <c r="B25" s="3">
         <v>2034724</v>
       </c>
-      <c r="C25" s="7">
+      <c r="C25" s="3">
         <v>2034739</v>
       </c>
       <c r="G25" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="15.95">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26" s="2"/>
-      <c r="B26" s="7">
+      <c r="B26" s="3">
         <v>2048240</v>
       </c>
-      <c r="C26" s="7">
+      <c r="C26" s="3">
         <v>2048439</v>
       </c>
       <c r="G26" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="15.95">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27" s="2"/>
-      <c r="B27" s="7">
+      <c r="B27" s="3">
         <v>1721480</v>
       </c>
-      <c r="C27" s="7">
+      <c r="C27" s="3">
         <v>1721598</v>
       </c>
       <c r="G27" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="15.95">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28" s="2"/>
-      <c r="B28" s="7">
+      <c r="B28" s="3">
         <v>1844799</v>
       </c>
-      <c r="C28" s="7">
+      <c r="C28" s="3">
         <v>1845000</v>
       </c>
       <c r="G28" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="29" spans="1:7" ht="15.95">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29" s="2"/>
-      <c r="B29" s="7">
+      <c r="B29" s="3">
         <v>1845001</v>
       </c>
-      <c r="C29" s="7">
+      <c r="C29" s="3">
         <v>1845298</v>
       </c>
       <c r="G29" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="30" spans="1:7" ht="15.95">
-      <c r="A30" s="5"/>
-      <c r="B30" s="8">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A30" s="2"/>
+      <c r="B30" s="3">
         <v>206001</v>
       </c>
-      <c r="C30" s="8">
+      <c r="C30" s="3">
         <v>206376</v>
       </c>
       <c r="G30" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="31" spans="1:7" ht="15.95">
-      <c r="A31" s="5"/>
-      <c r="B31" s="8">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A31" s="2"/>
+      <c r="B31" s="3">
         <v>206384</v>
       </c>
-      <c r="C31" s="8">
+      <c r="C31" s="3">
         <v>206590</v>
       </c>
       <c r="G31" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="32" spans="1:7" ht="15.95">
-      <c r="A32" s="5"/>
-      <c r="B32" s="6">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A32" s="2"/>
+      <c r="B32" s="5">
         <v>357130</v>
       </c>
-      <c r="C32" s="7">
+      <c r="C32" s="3">
         <v>357677</v>
       </c>
       <c r="G32" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="33" spans="1:7" ht="15.95">
-      <c r="A33" s="5"/>
-      <c r="B33" s="7">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A33" s="2"/>
+      <c r="B33" s="3">
         <v>356178</v>
       </c>
-      <c r="C33" s="7">
+      <c r="C33" s="3">
         <v>357677</v>
       </c>
       <c r="G33" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="34" spans="1:7" ht="15.95">
-      <c r="A34" s="5"/>
-      <c r="B34" s="7">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A34" s="2"/>
+      <c r="B34" s="3">
         <v>363183</v>
       </c>
-      <c r="C34" s="7">
+      <c r="C34" s="3">
         <v>364682</v>
       </c>
       <c r="G34" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="35" spans="1:7" ht="15.95">
-      <c r="A35" s="5"/>
-      <c r="B35" s="7">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A35" s="2"/>
+      <c r="B35" s="3">
         <v>365153</v>
       </c>
-      <c r="C35" s="7">
+      <c r="C35" s="3">
         <v>366050</v>
       </c>
       <c r="G35" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="36" spans="1:7" ht="15.95">
-      <c r="A36" s="5"/>
-      <c r="B36" s="7">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A36" s="2"/>
+      <c r="B36" s="3">
         <v>366051</v>
       </c>
-      <c r="C36" s="7">
+      <c r="C36" s="3">
         <v>366652</v>
       </c>
       <c r="G36" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="37" spans="1:7" ht="15.95">
-      <c r="A37" s="5"/>
-      <c r="B37" s="7">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A37" s="2"/>
+      <c r="B37" s="3">
         <v>368453</v>
       </c>
-      <c r="C37" s="7">
+      <c r="C37" s="3">
         <v>369050</v>
       </c>
       <c r="G37" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="38" spans="1:7" ht="15.95">
-      <c r="A38" s="5"/>
-      <c r="B38" s="7">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A38" s="2"/>
+      <c r="B38" s="3">
         <v>369051</v>
       </c>
-      <c r="C38" s="7">
+      <c r="C38" s="3">
         <v>369952</v>
       </c>
       <c r="G38" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="39" spans="1:7" ht="15.95">
-      <c r="A39" s="5"/>
-      <c r="B39" s="7">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A39" s="2"/>
+      <c r="B39" s="3">
         <v>138680</v>
       </c>
-      <c r="C39" s="7">
+      <c r="C39" s="3">
         <v>139019</v>
       </c>
       <c r="G39" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="40" spans="1:7" ht="15.95">
-      <c r="A40" s="5"/>
-      <c r="B40" s="7">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A40" s="2"/>
+      <c r="B40" s="3">
         <v>141020</v>
       </c>
-      <c r="C40" s="7">
+      <c r="C40" s="3">
         <v>142019</v>
       </c>
       <c r="G40" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="41" spans="1:7" ht="15.95">
-      <c r="A41" s="5"/>
-      <c r="B41" s="7">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A41" s="2"/>
+      <c r="B41" s="3">
         <v>142020</v>
       </c>
-      <c r="C41" s="7">
+      <c r="C41" s="3">
         <v>143019</v>
       </c>
       <c r="G41" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="42" spans="1:7">
-      <c r="A42" s="49"/>
-      <c r="B42" s="49"/>
-      <c r="C42" s="49"/>
-      <c r="D42" s="49"/>
-      <c r="E42" s="49"/>
-      <c r="F42" s="49"/>
-      <c r="G42" s="49"/>
-    </row>
-    <row r="43" spans="1:7">
-      <c r="A43" s="49"/>
-      <c r="B43" s="49"/>
-      <c r="C43" s="49"/>
-      <c r="D43" s="49"/>
-      <c r="E43" s="49"/>
-      <c r="F43" s="49"/>
-      <c r="G43" s="49"/>
-    </row>
-    <row r="44" spans="1:7">
-      <c r="A44" s="49"/>
-      <c r="B44" s="49"/>
-      <c r="C44" s="49"/>
-      <c r="D44" s="49"/>
-      <c r="E44" s="49"/>
-      <c r="F44" s="49"/>
-      <c r="G44" s="49"/>
-    </row>
-    <row r="45" spans="1:7">
-      <c r="A45" s="49"/>
-      <c r="B45" s="49"/>
-      <c r="C45" s="49"/>
-      <c r="D45" s="49"/>
-      <c r="E45" s="49"/>
-      <c r="F45" s="49"/>
-      <c r="G45" s="49"/>
-    </row>
-    <row r="46" spans="1:7">
-      <c r="A46" s="49"/>
-      <c r="B46" s="49"/>
-      <c r="C46" s="49"/>
-      <c r="D46" s="49"/>
-      <c r="E46" s="49"/>
-      <c r="F46" s="49"/>
-      <c r="G46" s="49"/>
-    </row>
-    <row r="47" spans="1:7">
-      <c r="A47" s="49"/>
-      <c r="B47" s="49"/>
-      <c r="C47" s="49"/>
-      <c r="D47" s="49"/>
-      <c r="E47" s="49"/>
-      <c r="F47" s="49"/>
-      <c r="G47" s="49"/>
-    </row>
-    <row r="48" spans="1:7">
-      <c r="A48" s="49"/>
-      <c r="B48" s="49"/>
-      <c r="C48" s="49"/>
-      <c r="D48" s="49"/>
-      <c r="E48" s="49"/>
-      <c r="F48" s="49"/>
-      <c r="G48" s="49"/>
-    </row>
-    <row r="49" spans="1:7">
-      <c r="A49" s="49"/>
-      <c r="B49" s="49"/>
-      <c r="C49" s="49"/>
-      <c r="D49" s="49"/>
-      <c r="E49" s="49"/>
-      <c r="F49" s="49"/>
-      <c r="G49" s="49"/>
-    </row>
-    <row r="50" spans="1:7">
-      <c r="A50" s="49"/>
-      <c r="B50" s="49"/>
-      <c r="C50" s="49"/>
-      <c r="D50" s="49"/>
-      <c r="E50" s="49"/>
-      <c r="F50" s="49"/>
-      <c r="G50" s="49"/>
-    </row>
-    <row r="51" spans="1:7">
-      <c r="A51" s="49"/>
-      <c r="B51" s="49"/>
-      <c r="C51" s="49"/>
-      <c r="D51" s="49"/>
-      <c r="E51" s="49"/>
-      <c r="F51" s="49"/>
-      <c r="G51" s="49"/>
-    </row>
-    <row r="52" spans="1:7">
-      <c r="A52" s="49"/>
-      <c r="B52" s="49"/>
-      <c r="C52" s="49"/>
-      <c r="D52" s="49"/>
-      <c r="E52" s="49"/>
-      <c r="F52" s="49"/>
-      <c r="G52" s="49"/>
-    </row>
-    <row r="53" spans="1:7">
-      <c r="A53" s="49"/>
-      <c r="B53" s="49"/>
-      <c r="C53" s="49"/>
-      <c r="D53" s="49"/>
-      <c r="E53" s="49"/>
-      <c r="F53" s="49"/>
-      <c r="G53" s="49"/>
-    </row>
-    <row r="54" spans="1:7">
-      <c r="A54" s="49"/>
-      <c r="B54" s="49"/>
-      <c r="C54" s="49"/>
-      <c r="D54" s="49"/>
-      <c r="E54" s="49"/>
-      <c r="F54" s="49"/>
-      <c r="G54" s="49"/>
-    </row>
-    <row r="55" spans="1:7">
-      <c r="A55" s="49"/>
-      <c r="B55" s="49"/>
-      <c r="C55" s="49"/>
-      <c r="D55" s="49"/>
-      <c r="E55" s="49"/>
-      <c r="F55" s="49"/>
-      <c r="G55" s="49"/>
-    </row>
-    <row r="56" spans="1:7">
-      <c r="A56" s="49"/>
-      <c r="B56" s="49"/>
-      <c r="C56" s="49"/>
-      <c r="D56" s="49"/>
-      <c r="E56" s="49"/>
-      <c r="F56" s="49"/>
-      <c r="G56" s="49"/>
-    </row>
-    <row r="57" spans="1:7">
-      <c r="A57" s="49"/>
-      <c r="B57" s="49"/>
-      <c r="C57" s="49"/>
-      <c r="D57" s="49"/>
-      <c r="E57" s="49"/>
-      <c r="F57" s="49"/>
-      <c r="G57" s="49"/>
-    </row>
-    <row r="58" spans="1:7">
-      <c r="A58" s="49"/>
-      <c r="B58" s="49"/>
-      <c r="C58" s="49"/>
-      <c r="D58" s="49"/>
-      <c r="E58" s="49"/>
-      <c r="F58" s="49"/>
-      <c r="G58" s="49"/>
-    </row>
-    <row r="59" spans="1:7">
-      <c r="A59" s="49"/>
-      <c r="B59" s="49"/>
-      <c r="C59" s="49"/>
-      <c r="D59" s="49"/>
-      <c r="E59" s="49"/>
-      <c r="F59" s="49"/>
-      <c r="G59" s="49"/>
-    </row>
-    <row r="60" spans="1:7">
-      <c r="A60" s="49"/>
-      <c r="B60" s="49"/>
-      <c r="C60" s="49"/>
-      <c r="D60" s="49"/>
-      <c r="E60" s="49"/>
-      <c r="F60" s="49"/>
-      <c r="G60" s="49"/>
-    </row>
-    <row r="61" spans="1:7">
-      <c r="A61" s="49"/>
-      <c r="B61" s="49"/>
-      <c r="C61" s="49"/>
-      <c r="D61" s="49"/>
-      <c r="E61" s="49"/>
-      <c r="F61" s="49"/>
-      <c r="G61" s="49"/>
-    </row>
-    <row r="62" spans="1:7">
-      <c r="A62" s="49"/>
-      <c r="B62" s="49"/>
-      <c r="C62" s="49"/>
-      <c r="D62" s="49"/>
-      <c r="E62" s="49"/>
-      <c r="F62" s="49"/>
-      <c r="G62" s="49"/>
-    </row>
-    <row r="63" spans="1:7">
-      <c r="A63" s="49"/>
-      <c r="B63" s="49"/>
-      <c r="C63" s="49"/>
-      <c r="D63" s="49"/>
-      <c r="E63" s="49"/>
-      <c r="F63" s="49"/>
-      <c r="G63" s="49"/>
-    </row>
-    <row r="64" spans="1:7">
-      <c r="A64" s="49"/>
-      <c r="B64" s="49"/>
-      <c r="C64" s="49"/>
-      <c r="D64" s="49"/>
-      <c r="E64" s="49"/>
-      <c r="F64" s="49"/>
-      <c r="G64" s="49"/>
-    </row>
-    <row r="65" spans="1:7">
-      <c r="A65" s="49"/>
-      <c r="B65" s="49"/>
-      <c r="C65" s="49"/>
-      <c r="D65" s="49"/>
-      <c r="E65" s="49"/>
-      <c r="F65" s="49"/>
-      <c r="G65" s="49"/>
-    </row>
-    <row r="66" spans="1:7">
-      <c r="A66" s="49"/>
-      <c r="B66" s="49"/>
-      <c r="C66" s="49"/>
-      <c r="D66" s="49"/>
-      <c r="E66" s="49"/>
-      <c r="F66" s="49"/>
-      <c r="G66" s="49"/>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A42" s="46"/>
+      <c r="B42" s="46"/>
+      <c r="C42" s="46"/>
+      <c r="D42" s="46"/>
+      <c r="E42" s="46"/>
+      <c r="F42" s="46"/>
+      <c r="G42" s="46"/>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A43" s="46"/>
+      <c r="B43" s="46"/>
+      <c r="C43" s="46"/>
+      <c r="D43" s="46"/>
+      <c r="E43" s="46"/>
+      <c r="F43" s="46"/>
+      <c r="G43" s="46"/>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A44" s="46"/>
+      <c r="B44" s="46"/>
+      <c r="C44" s="46"/>
+      <c r="D44" s="46"/>
+      <c r="E44" s="46"/>
+      <c r="F44" s="46"/>
+      <c r="G44" s="46"/>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A45" s="46"/>
+      <c r="B45" s="46"/>
+      <c r="C45" s="46"/>
+      <c r="D45" s="46"/>
+      <c r="E45" s="46"/>
+      <c r="F45" s="46"/>
+      <c r="G45" s="46"/>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A46" s="46"/>
+      <c r="B46" s="46"/>
+      <c r="C46" s="46"/>
+      <c r="D46" s="46"/>
+      <c r="E46" s="46"/>
+      <c r="F46" s="46"/>
+      <c r="G46" s="46"/>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A47" s="46"/>
+      <c r="B47" s="46"/>
+      <c r="C47" s="46"/>
+      <c r="D47" s="46"/>
+      <c r="E47" s="46"/>
+      <c r="F47" s="46"/>
+      <c r="G47" s="46"/>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A48" s="46"/>
+      <c r="B48" s="46"/>
+      <c r="C48" s="46"/>
+      <c r="D48" s="46"/>
+      <c r="E48" s="46"/>
+      <c r="F48" s="46"/>
+      <c r="G48" s="46"/>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A49" s="46"/>
+      <c r="B49" s="46"/>
+      <c r="C49" s="46"/>
+      <c r="D49" s="46"/>
+      <c r="E49" s="46"/>
+      <c r="F49" s="46"/>
+      <c r="G49" s="46"/>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A50" s="46"/>
+      <c r="B50" s="46"/>
+      <c r="C50" s="46"/>
+      <c r="D50" s="46"/>
+      <c r="E50" s="46"/>
+      <c r="F50" s="46"/>
+      <c r="G50" s="46"/>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A51" s="46"/>
+      <c r="B51" s="46"/>
+      <c r="C51" s="46"/>
+      <c r="D51" s="46"/>
+      <c r="E51" s="46"/>
+      <c r="F51" s="46"/>
+      <c r="G51" s="46"/>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A52" s="46"/>
+      <c r="B52" s="46"/>
+      <c r="C52" s="46"/>
+      <c r="D52" s="46"/>
+      <c r="E52" s="46"/>
+      <c r="F52" s="46"/>
+      <c r="G52" s="46"/>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A53" s="46"/>
+      <c r="B53" s="46"/>
+      <c r="C53" s="46"/>
+      <c r="D53" s="46"/>
+      <c r="E53" s="46"/>
+      <c r="F53" s="46"/>
+      <c r="G53" s="46"/>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A54" s="46"/>
+      <c r="B54" s="46"/>
+      <c r="C54" s="46"/>
+      <c r="D54" s="46"/>
+      <c r="E54" s="46"/>
+      <c r="F54" s="46"/>
+      <c r="G54" s="46"/>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A55" s="46"/>
+      <c r="B55" s="46"/>
+      <c r="C55" s="46"/>
+      <c r="D55" s="46"/>
+      <c r="E55" s="46"/>
+      <c r="F55" s="46"/>
+      <c r="G55" s="46"/>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A56" s="46"/>
+      <c r="B56" s="46"/>
+      <c r="C56" s="46"/>
+      <c r="D56" s="46"/>
+      <c r="E56" s="46"/>
+      <c r="F56" s="46"/>
+      <c r="G56" s="46"/>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A57" s="46"/>
+      <c r="B57" s="46"/>
+      <c r="C57" s="46"/>
+      <c r="D57" s="46"/>
+      <c r="E57" s="46"/>
+      <c r="F57" s="46"/>
+      <c r="G57" s="46"/>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A58" s="46"/>
+      <c r="B58" s="46"/>
+      <c r="C58" s="46"/>
+      <c r="D58" s="46"/>
+      <c r="E58" s="46"/>
+      <c r="F58" s="46"/>
+      <c r="G58" s="46"/>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A59" s="46"/>
+      <c r="B59" s="46"/>
+      <c r="C59" s="46"/>
+      <c r="D59" s="46"/>
+      <c r="E59" s="46"/>
+      <c r="F59" s="46"/>
+      <c r="G59" s="46"/>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A60" s="46"/>
+      <c r="B60" s="46"/>
+      <c r="C60" s="46"/>
+      <c r="D60" s="46"/>
+      <c r="E60" s="46"/>
+      <c r="F60" s="46"/>
+      <c r="G60" s="46"/>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A61" s="46"/>
+      <c r="B61" s="46"/>
+      <c r="C61" s="46"/>
+      <c r="D61" s="46"/>
+      <c r="E61" s="46"/>
+      <c r="F61" s="46"/>
+      <c r="G61" s="46"/>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A62" s="46"/>
+      <c r="B62" s="46"/>
+      <c r="C62" s="46"/>
+      <c r="D62" s="46"/>
+      <c r="E62" s="46"/>
+      <c r="F62" s="46"/>
+      <c r="G62" s="46"/>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A63" s="46"/>
+      <c r="B63" s="46"/>
+      <c r="C63" s="46"/>
+      <c r="D63" s="46"/>
+      <c r="E63" s="46"/>
+      <c r="F63" s="46"/>
+      <c r="G63" s="46"/>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A64" s="46"/>
+      <c r="B64" s="46"/>
+      <c r="C64" s="46"/>
+      <c r="D64" s="46"/>
+      <c r="E64" s="46"/>
+      <c r="F64" s="46"/>
+      <c r="G64" s="46"/>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A65" s="46"/>
+      <c r="B65" s="46"/>
+      <c r="C65" s="46"/>
+      <c r="D65" s="46"/>
+      <c r="E65" s="46"/>
+      <c r="F65" s="46"/>
+      <c r="G65" s="46"/>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A66" s="46"/>
+      <c r="B66" s="46"/>
+      <c r="C66" s="46"/>
+      <c r="D66" s="46"/>
+      <c r="E66" s="46"/>
+      <c r="F66" s="46"/>
+      <c r="G66" s="46"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1650,181 +1651,181 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:H54"/>
-  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="22" style="15" customWidth="1"/>
-    <col min="2" max="5" width="10.77734375" style="15"/>
-    <col min="6" max="6" width="20.109375" style="15" customWidth="1"/>
-    <col min="7" max="7" width="39.88671875" style="15" customWidth="1"/>
-    <col min="8" max="8" width="32.77734375" style="15" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="22" style="12" customWidth="1"/>
+    <col min="2" max="5" width="10.83203125" style="12"/>
+    <col min="6" max="6" width="20.1640625" style="12" customWidth="1"/>
+    <col min="7" max="7" width="39.83203125" style="12" customWidth="1"/>
+    <col min="8" max="8" width="32.83203125" style="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="15.75">
-      <c r="A1" s="14" t="s">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="B1" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="14" t="s">
+      <c r="C1" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="14" t="s">
+      <c r="D1" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="14" t="s">
+      <c r="E1" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="14" t="s">
+      <c r="F1" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="14" t="s">
+      <c r="G1" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="14" t="s">
+      <c r="H1" s="11" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
-      <c r="A2" s="9">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A2" s="6">
         <v>2080080000000</v>
       </c>
-      <c r="B2" s="16">
+      <c r="B2" s="13">
         <v>2027654</v>
       </c>
-      <c r="C2" s="16">
+      <c r="C2" s="13">
         <v>2027785</v>
       </c>
-      <c r="F2" s="15" t="s">
+      <c r="F2" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="G2" s="15" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8">
-      <c r="A3" s="9">
+      <c r="G2" s="12" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A3" s="6">
         <v>2080100000000</v>
       </c>
-      <c r="B3" s="16">
+      <c r="B3" s="13">
         <v>2028008</v>
       </c>
-      <c r="C3" s="16">
+      <c r="C3" s="13">
         <v>2028895</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G3" s="15" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
-      <c r="A4" s="9">
+      <c r="G3" s="12" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A4" s="6">
         <v>2080100000000</v>
       </c>
-      <c r="B4" s="15">
+      <c r="B4" s="12">
         <v>1998669</v>
       </c>
-      <c r="C4" s="15">
+      <c r="C4" s="12">
         <v>1998675</v>
       </c>
       <c r="F4" t="s">
         <v>9</v>
       </c>
-      <c r="G4" s="15" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
-      <c r="A5" s="9">
+      <c r="G4" s="12" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A5" s="6">
         <v>2080120000000</v>
       </c>
-      <c r="B5" s="16">
+      <c r="B5" s="13">
         <v>2025119</v>
       </c>
-      <c r="C5" s="16">
+      <c r="C5" s="13">
         <v>2025799</v>
       </c>
       <c r="F5" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="G5" s="15" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8">
-      <c r="A6" s="9">
+      <c r="G5" s="12" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A6" s="6">
         <v>2080120000000</v>
       </c>
-      <c r="B6" s="16">
+      <c r="B6" s="13">
         <v>2025800</v>
       </c>
-      <c r="C6" s="16">
+      <c r="C6" s="13">
         <v>2026799</v>
       </c>
       <c r="F6" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="G6" s="15" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8">
-      <c r="A7" s="9">
+      <c r="G6" s="12" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A7" s="6">
         <v>2080130200000</v>
       </c>
-      <c r="B7" s="16">
+      <c r="B7" s="13">
         <v>2027016</v>
       </c>
-      <c r="C7" s="16">
+      <c r="C7" s="13">
         <v>2027515</v>
       </c>
       <c r="F7" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="G7" s="15" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8">
-      <c r="A8" s="9">
+      <c r="G7" s="12" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A8" s="6">
         <v>2080130200000</v>
       </c>
-      <c r="B8" s="16">
+      <c r="B8" s="13">
         <v>2028896</v>
       </c>
-      <c r="C8" s="16">
+      <c r="C8" s="13">
         <v>2028900</v>
       </c>
       <c r="F8" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="G8" s="15" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8">
-      <c r="A9" s="15" t="s">
+      <c r="G8" s="12" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A9" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="B9" s="16">
+      <c r="B9" s="13">
         <v>2027534</v>
       </c>
-      <c r="C9" s="16">
+      <c r="C9" s="13">
         <v>2027653</v>
       </c>
-      <c r="F9" s="15" t="s">
+      <c r="F9" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="G9" s="15" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8">
-      <c r="A10" s="9">
+      <c r="G9" s="12" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A10" s="6">
         <v>2080100000000</v>
       </c>
       <c r="B10" s="3">
@@ -1836,12 +1837,12 @@
       <c r="F10" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="G10" s="15" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8">
-      <c r="A11" s="9">
+      <c r="G10" s="12" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A11" s="6">
         <v>2080100000000</v>
       </c>
       <c r="B11" s="3">
@@ -1853,12 +1854,12 @@
       <c r="F11" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="G11" s="15" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8">
-      <c r="A12" s="9">
+      <c r="G11" s="12" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A12" s="6">
         <v>2080100000000</v>
       </c>
       <c r="B12" s="3">
@@ -1870,12 +1871,12 @@
       <c r="F12" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="G12" s="15" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8">
-      <c r="A13" s="9">
+      <c r="G12" s="12" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A13" s="6">
         <v>2080100000000</v>
       </c>
       <c r="B13" s="3">
@@ -1887,12 +1888,12 @@
       <c r="F13" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="G13" s="15" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8">
-      <c r="A14" s="9">
+      <c r="G13" s="12" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A14" s="6">
         <v>2080100000000</v>
       </c>
       <c r="B14" s="3">
@@ -1904,12 +1905,12 @@
       <c r="F14" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="G14" s="15" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8">
-      <c r="A15" s="9">
+      <c r="G14" s="12" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A15" s="6">
         <v>2080130200000</v>
       </c>
       <c r="B15" s="3">
@@ -1921,12 +1922,12 @@
       <c r="F15" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="G15" s="15" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8">
-      <c r="A16" s="9">
+      <c r="G15" s="12" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A16" s="6">
         <v>2080130200000</v>
       </c>
       <c r="B16" s="3">
@@ -1938,12 +1939,12 @@
       <c r="F16" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="G16" s="15" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17" s="9">
+      <c r="G16" s="12" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A17" s="6">
         <v>2080130200000</v>
       </c>
       <c r="B17" s="3">
@@ -1955,29 +1956,29 @@
       <c r="F17" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G17" s="15" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18" s="9">
+      <c r="G17" s="12" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A18" s="6">
         <v>2080130200000</v>
       </c>
-      <c r="B18" s="17">
+      <c r="B18" s="14">
         <v>2033310</v>
       </c>
-      <c r="C18" s="17">
+      <c r="C18" s="14">
         <v>2033799</v>
       </c>
-      <c r="F18" s="18" t="s">
+      <c r="F18" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="G18" s="15" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19" s="9">
+      <c r="G18" s="12" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A19" s="6">
         <v>2080130200000</v>
       </c>
       <c r="B19" s="3">
@@ -1986,32 +1987,32 @@
       <c r="C19" s="3">
         <v>2033809</v>
       </c>
-      <c r="F19" s="18" t="s">
+      <c r="F19" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="G19" s="15" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" ht="15.75">
-      <c r="A20" s="9">
+      <c r="G19" s="12" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A20" s="6">
         <v>2080150200000</v>
       </c>
-      <c r="B20" s="19">
+      <c r="B20" s="16">
         <v>2032800</v>
       </c>
-      <c r="C20" s="10">
+      <c r="C20" s="7">
         <v>2033159</v>
       </c>
-      <c r="F20" s="19" t="s">
+      <c r="F20" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="G20" s="15" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21" s="15" t="s">
+      <c r="G20" s="12" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A21" s="12" t="s">
         <v>29</v>
       </c>
       <c r="B21" s="3">
@@ -2021,151 +2022,151 @@
       <c r="C21" s="3">
         <v>2033309</v>
       </c>
-      <c r="F21" s="15" t="s">
+      <c r="F21" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="G21" s="15" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" ht="15.75">
-      <c r="A22" s="20">
+      <c r="G21" s="12" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A22" s="17">
         <v>2080060000000</v>
       </c>
-      <c r="B22" s="19">
+      <c r="B22" s="16">
         <v>2024666</v>
       </c>
-      <c r="C22" s="10">
+      <c r="C22" s="7">
         <v>2024689</v>
       </c>
       <c r="F22" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="G22" s="15" t="s">
+      <c r="G22" s="12" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="16.5" thickBot="1">
-      <c r="A23" s="21">
+    <row r="23" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="18">
         <v>2080070000000</v>
       </c>
-      <c r="B23" s="23">
+      <c r="B23" s="20">
         <v>2024690</v>
       </c>
-      <c r="C23" s="24">
+      <c r="C23" s="21">
         <v>2024699</v>
       </c>
-      <c r="F23" s="25" t="s">
+      <c r="F23" s="22" t="s">
         <v>32</v>
       </c>
-      <c r="G23" s="15" t="s">
+      <c r="G23" s="12" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="16.5" thickTop="1">
-      <c r="A24" s="22">
+    <row r="24" spans="1:7" ht="17" thickTop="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="19">
         <v>2080070000000</v>
       </c>
-      <c r="B24" s="13">
+      <c r="B24" s="10">
         <v>2047740</v>
       </c>
-      <c r="C24" s="11">
+      <c r="C24" s="8">
         <v>2047844</v>
       </c>
-      <c r="F24" s="12" t="s">
+      <c r="F24" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="G24" s="15" t="s">
+      <c r="G24" s="12" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="15.75">
-      <c r="A25" s="22">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A25" s="19">
         <v>2080070000000</v>
       </c>
-      <c r="B25" s="13">
+      <c r="B25" s="10">
         <v>2047845</v>
       </c>
-      <c r="C25" s="11">
+      <c r="C25" s="8">
         <v>2047994</v>
       </c>
       <c r="F25" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="G25" s="15" t="s">
+      <c r="G25" s="12" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="15.75">
-      <c r="A26" s="22">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A26" s="19">
         <v>2080070000000</v>
       </c>
-      <c r="B26" s="13">
+      <c r="B26" s="10">
         <v>2048195</v>
       </c>
-      <c r="C26" s="11">
+      <c r="C26" s="8">
         <v>2048239</v>
       </c>
       <c r="F26" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="G26" s="15" t="s">
+      <c r="G26" s="12" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="15.75">
-      <c r="A27" s="22">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A27" s="19">
         <v>2080070000000</v>
       </c>
-      <c r="B27" s="13">
+      <c r="B27" s="10">
         <v>2058440</v>
       </c>
-      <c r="C27" s="11">
+      <c r="C27" s="8">
         <v>2058494</v>
       </c>
       <c r="F27" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="G27" s="15" t="s">
+      <c r="G27" s="12" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="15.75">
-      <c r="A28" s="22">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A28" s="19">
         <v>2080060000000</v>
       </c>
-      <c r="B28" s="13">
+      <c r="B28" s="10">
         <v>2047995</v>
       </c>
-      <c r="C28" s="11">
+      <c r="C28" s="8">
         <v>2048094</v>
       </c>
       <c r="F28" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="G28" s="15" t="s">
+      <c r="G28" s="12" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="29" spans="1:7" ht="15.75">
-      <c r="A29" s="22">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A29" s="19">
         <v>2080060000000</v>
       </c>
-      <c r="B29" s="13">
+      <c r="B29" s="10">
         <v>2048095</v>
       </c>
-      <c r="C29" s="11">
+      <c r="C29" s="8">
         <v>2048194</v>
       </c>
       <c r="F29" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="G29" s="15" t="s">
+      <c r="G29" s="12" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="30" spans="1:7">
-      <c r="A30" s="26">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A30" s="23">
         <v>2080170200000</v>
       </c>
       <c r="B30" s="3">
@@ -2177,12 +2178,12 @@
       <c r="F30" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="G30" s="15" t="s">
+      <c r="G30" s="12" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="31" spans="1:7">
-      <c r="A31" s="26">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A31" s="23">
         <v>2080170200000</v>
       </c>
       <c r="B31" s="3">
@@ -2194,12 +2195,12 @@
       <c r="F31" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="G31" s="15" t="s">
+      <c r="G31" s="12" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="32" spans="1:7">
-      <c r="A32" s="26">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A32" s="23">
         <v>2080170200000</v>
       </c>
       <c r="B32" s="3">
@@ -2211,12 +2212,12 @@
       <c r="F32" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="G32" s="15" t="s">
+      <c r="G32" s="12" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="33" spans="1:8">
-      <c r="A33" s="27" t="s">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A33" s="24" t="s">
         <v>38</v>
       </c>
       <c r="B33" s="3">
@@ -2228,250 +2229,250 @@
       <c r="F33" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="G33" s="15" t="s">
+      <c r="G33" s="12" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="34" spans="1:8" ht="15.75">
-      <c r="A34" s="15" t="s">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A34" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="B34" s="19">
+      <c r="B34" s="16">
         <v>357105</v>
       </c>
-      <c r="C34" s="10">
+      <c r="C34" s="7">
         <v>357129</v>
       </c>
       <c r="F34" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="G34" s="15" t="s">
+      <c r="G34" s="12" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="35" spans="1:8" ht="15.75">
-      <c r="A35" s="15" t="s">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A35" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="B35" s="13">
+      <c r="B35" s="10">
         <v>357080</v>
       </c>
-      <c r="C35" s="11">
+      <c r="C35" s="8">
         <v>357104</v>
       </c>
       <c r="F35" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="G35" s="15" t="s">
+      <c r="G35" s="12" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="36" spans="1:8" ht="15.75">
-      <c r="A36" s="15" t="s">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A36" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="B36" s="13">
+      <c r="B36" s="10">
         <v>357055</v>
       </c>
-      <c r="C36" s="11">
+      <c r="C36" s="8">
         <v>357079</v>
       </c>
       <c r="F36" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="G36" s="15" t="s">
+      <c r="G36" s="12" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="37" spans="1:8" ht="15.75">
-      <c r="A37" s="15" t="s">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A37" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="B37" s="13">
+      <c r="B37" s="10">
         <v>357030</v>
       </c>
-      <c r="C37" s="11">
+      <c r="C37" s="8">
         <v>357054</v>
       </c>
       <c r="F37" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="G37" s="15" t="s">
+      <c r="G37" s="12" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="38" spans="1:8" ht="15.75">
-      <c r="A38" s="15" t="s">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A38" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="B38" s="13">
+      <c r="B38" s="10">
         <v>357005</v>
       </c>
-      <c r="C38" s="11">
+      <c r="C38" s="8">
         <v>357029</v>
       </c>
       <c r="F38" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="G38" s="15" t="s">
+      <c r="G38" s="12" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="39" spans="1:8" ht="15.75">
-      <c r="A39" s="15" t="s">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A39" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="B39" s="13">
+      <c r="B39" s="10">
         <v>356980</v>
       </c>
-      <c r="C39" s="11">
+      <c r="C39" s="8">
         <v>357004</v>
       </c>
       <c r="F39" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="G39" s="15" t="s">
+      <c r="G39" s="12" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="40" spans="1:8" ht="15.75">
-      <c r="A40" s="15" t="s">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A40" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="B40" s="13">
+      <c r="B40" s="10">
         <v>356955</v>
       </c>
-      <c r="C40" s="11">
+      <c r="C40" s="8">
         <v>356979</v>
       </c>
       <c r="F40" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="G40" s="15" t="s">
+      <c r="G40" s="12" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="41" spans="1:8" ht="15.75">
-      <c r="A41" s="15" t="s">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A41" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="B41" s="13">
+      <c r="B41" s="10">
         <v>356930</v>
       </c>
-      <c r="C41" s="11">
+      <c r="C41" s="8">
         <v>356954</v>
       </c>
       <c r="F41" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="G41" s="15" t="s">
+      <c r="G41" s="12" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="42" spans="1:8" ht="15.75">
-      <c r="A42" s="15" t="s">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A42" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="B42" s="13">
+      <c r="B42" s="10">
         <v>356905</v>
       </c>
-      <c r="C42" s="11">
+      <c r="C42" s="8">
         <v>356929</v>
       </c>
       <c r="F42" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="G42" s="15" t="s">
+      <c r="G42" s="12" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="43" spans="1:8" ht="15.75">
-      <c r="A43" s="15" t="s">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A43" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="B43" s="13">
+      <c r="B43" s="10">
         <v>356880</v>
       </c>
-      <c r="C43" s="11">
+      <c r="C43" s="8">
         <v>356904</v>
       </c>
       <c r="F43" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="G43" s="15" t="s">
+      <c r="G43" s="12" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="44" spans="1:8" ht="15.75">
-      <c r="A44" s="15" t="s">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A44" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="B44" s="13">
+      <c r="B44" s="10">
         <v>356855</v>
       </c>
-      <c r="C44" s="11">
+      <c r="C44" s="8">
         <v>356879</v>
       </c>
       <c r="F44" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="G44" s="15" t="s">
+      <c r="G44" s="12" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="45" spans="1:8" ht="15.75">
-      <c r="A45" s="15" t="s">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A45" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="B45" s="13">
+      <c r="B45" s="10">
         <v>356830</v>
       </c>
-      <c r="C45" s="11">
+      <c r="C45" s="8">
         <v>356854</v>
       </c>
       <c r="F45" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="G45" s="15" t="s">
+      <c r="G45" s="12" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="46" spans="1:8" ht="15.75">
-      <c r="A46" s="15" t="s">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A46" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="B46" s="13">
+      <c r="B46" s="10">
         <v>356805</v>
       </c>
-      <c r="C46" s="11">
+      <c r="C46" s="8">
         <v>356829</v>
       </c>
       <c r="F46" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="G46" s="15" t="s">
+      <c r="G46" s="12" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="47" spans="1:8">
-      <c r="A47" s="15" t="s">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A47" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="B47" s="15" t="s">
+      <c r="B47" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="C47" s="15" t="s">
+      <c r="C47" s="12" t="s">
         <v>44</v>
       </c>
       <c r="F47" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="G47" s="15" t="s">
+      <c r="G47" s="12" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="48" spans="1:8">
-      <c r="A48" s="15" t="s">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A48" s="12" t="s">
         <v>45</v>
       </c>
       <c r="B48" s="3">
@@ -2480,7 +2481,7 @@
       <c r="C48" s="3">
         <v>138679</v>
       </c>
-      <c r="F48" s="55" t="s">
+      <c r="F48" s="52" t="s">
         <v>71</v>
       </c>
       <c r="G48" t="s">
@@ -2490,107 +2491,107 @@
         <v>72</v>
       </c>
     </row>
-    <row r="49" spans="1:7">
-      <c r="A49" s="52">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A49" s="49">
         <v>2080100000000</v>
       </c>
-      <c r="B49" s="51">
+      <c r="B49" s="48">
         <v>2033810</v>
       </c>
-      <c r="C49" s="51">
+      <c r="C49" s="48">
         <v>2034031</v>
       </c>
-      <c r="D49" s="53"/>
-      <c r="E49" s="53"/>
-      <c r="F49" s="51" t="s">
+      <c r="D49" s="50"/>
+      <c r="E49" s="50"/>
+      <c r="F49" s="48" t="s">
         <v>67</v>
       </c>
-      <c r="G49" s="50" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7">
-      <c r="A50" s="52">
+      <c r="G49" s="47" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A50" s="49">
         <v>2080100000000</v>
       </c>
-      <c r="B50" s="51">
+      <c r="B50" s="48">
         <v>2034032</v>
       </c>
-      <c r="C50" s="51">
+      <c r="C50" s="48">
         <v>2034159</v>
       </c>
-      <c r="F50" s="51" t="s">
+      <c r="F50" s="48" t="s">
         <v>67</v>
       </c>
-      <c r="G50" s="50" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7">
-      <c r="A51" s="52">
+      <c r="G50" s="47" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A51" s="49">
         <v>2080100000000</v>
       </c>
-      <c r="B51" s="54">
+      <c r="B51" s="51">
         <v>2034160</v>
       </c>
-      <c r="C51" s="54">
+      <c r="C51" s="51">
         <v>2034475</v>
       </c>
-      <c r="F51" s="51" t="s">
+      <c r="F51" s="48" t="s">
         <v>67</v>
       </c>
-      <c r="G51" s="50" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7">
-      <c r="A52" s="52">
+      <c r="G51" s="47" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A52" s="49">
         <v>2080120000000</v>
       </c>
-      <c r="B52" s="51">
+      <c r="B52" s="48">
         <v>2028901</v>
       </c>
-      <c r="C52" s="51">
+      <c r="C52" s="48">
         <v>2029100</v>
       </c>
-      <c r="F52" s="51" t="s">
+      <c r="F52" s="48" t="s">
         <v>68</v>
       </c>
-      <c r="G52" s="50" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7">
-      <c r="A53" s="52">
+      <c r="G52" s="47" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A53" s="49">
         <v>2080120000000</v>
       </c>
-      <c r="B53" s="51">
+      <c r="B53" s="48">
         <v>2029101</v>
       </c>
-      <c r="C53" s="51">
+      <c r="C53" s="48">
         <v>2029580</v>
       </c>
-      <c r="F53" s="51" t="s">
+      <c r="F53" s="48" t="s">
         <v>69</v>
       </c>
-      <c r="G53" s="50" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7">
-      <c r="A54" s="52">
+      <c r="G53" s="47" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A54" s="49">
         <v>2080150200000</v>
       </c>
-      <c r="B54" s="51">
+      <c r="B54" s="48">
         <v>2034476</v>
       </c>
-      <c r="C54" s="51">
+      <c r="C54" s="48">
         <v>2034595</v>
       </c>
-      <c r="F54" s="51" t="s">
+      <c r="F54" s="48" t="s">
         <v>70</v>
       </c>
-      <c r="G54" s="50" t="s">
+      <c r="G54" s="47" t="s">
         <v>6</v>
       </c>
     </row>
@@ -2601,39 +2602,39 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:G156"/>
-  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="17.77734375" customWidth="1"/>
+    <col min="1" max="1" width="17.83203125" customWidth="1"/>
     <col min="7" max="7" width="48" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="15.75">
-      <c r="A1" s="29" t="s">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="29" t="s">
+      <c r="B1" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="29" t="s">
+      <c r="C1" s="26" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="29" t="s">
+      <c r="D1" s="26" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="29" t="s">
+      <c r="E1" s="26" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="29" t="s">
+      <c r="F1" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="29" t="s">
+      <c r="G1" s="26" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="15.95">
-      <c r="A2" s="26">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2" s="23">
         <v>2080080000000</v>
       </c>
       <c r="B2" s="3">
@@ -2649,8 +2650,8 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="15.95">
-      <c r="A3" s="26">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A3" s="23">
         <v>2080080000000</v>
       </c>
       <c r="B3" s="3">
@@ -2666,8 +2667,8 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="15.95">
-      <c r="A4" s="26">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A4" s="23">
         <v>2080080000000</v>
       </c>
       <c r="B4" s="3">
@@ -2683,8 +2684,8 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="15.95">
-      <c r="A5" s="26">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A5" s="23">
         <v>2080080000000</v>
       </c>
       <c r="B5" s="3">
@@ -2700,8 +2701,8 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="15.95">
-      <c r="A6" s="26">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A6" s="23">
         <v>2080080000000</v>
       </c>
       <c r="B6" s="3">
@@ -2717,8 +2718,8 @@
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="15.95">
-      <c r="A7" s="26">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A7" s="23">
         <v>2080080000000</v>
       </c>
       <c r="B7" s="3">
@@ -2734,8 +2735,8 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="15.75">
-      <c r="A8" s="30">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A8" s="27">
         <v>2080100000000</v>
       </c>
       <c r="B8" s="3">
@@ -2751,8 +2752,8 @@
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="15.75">
-      <c r="A9" s="31">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A9" s="28">
         <v>2080100000000</v>
       </c>
       <c r="B9" s="3">
@@ -2768,8 +2769,8 @@
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="15.75">
-      <c r="A10" s="31">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A10" s="28">
         <v>2080100000000</v>
       </c>
       <c r="B10" s="3">
@@ -2785,8 +2786,8 @@
         <v>6</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="15.75">
-      <c r="A11" s="32">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A11" s="29">
         <v>2080100000001</v>
       </c>
       <c r="B11" s="3">
@@ -2802,8 +2803,8 @@
         <v>6</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="15.95">
-      <c r="A12" s="26">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A12" s="23">
         <v>2080120000000</v>
       </c>
       <c r="B12" s="3">
@@ -2819,25 +2820,25 @@
         <v>6</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="15.95">
-      <c r="A13" s="33">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A13" s="30">
         <v>2080120000000</v>
       </c>
-      <c r="B13" s="34">
+      <c r="B13" s="31">
         <v>2009944</v>
       </c>
-      <c r="C13" s="34">
+      <c r="C13" s="31">
         <v>2009945</v>
       </c>
-      <c r="D13" s="34" t="s">
+      <c r="D13" s="31" t="s">
         <v>49</v>
       </c>
       <c r="G13" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="15.95">
-      <c r="A14" s="26">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A14" s="23">
         <v>20801200000001</v>
       </c>
       <c r="B14" s="3">
@@ -2853,8 +2854,8 @@
         <v>6</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="15.95">
-      <c r="A15" s="26">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A15" s="23">
         <v>20801200000001</v>
       </c>
       <c r="B15" s="3">
@@ -2870,8 +2871,8 @@
         <v>6</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="15.95">
-      <c r="A16" s="26">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A16" s="23">
         <v>20801200000001</v>
       </c>
       <c r="B16" s="3">
@@ -2887,8 +2888,8 @@
         <v>6</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="15.95">
-      <c r="A17" s="26">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A17" s="23">
         <v>20801200000001</v>
       </c>
       <c r="B17" s="3">
@@ -2904,8 +2905,8 @@
         <v>6</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="15.75">
-      <c r="A18" s="30">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A18" s="27">
         <v>2080130200000</v>
       </c>
       <c r="B18" s="3">
@@ -2921,8 +2922,8 @@
         <v>6</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="15.75">
-      <c r="A19" s="31">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A19" s="28">
         <v>2080130200000</v>
       </c>
       <c r="B19" s="3">
@@ -2938,8 +2939,8 @@
         <v>6</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="15.75">
-      <c r="A20" s="31">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A20" s="28">
         <v>2080130200000</v>
       </c>
       <c r="B20" s="3">
@@ -2955,8 +2956,8 @@
         <v>6</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="15.75">
-      <c r="A21" s="31">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A21" s="28">
         <v>2080130200000</v>
       </c>
       <c r="B21" s="3">
@@ -2972,8 +2973,8 @@
         <v>6</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="15.75">
-      <c r="A22" s="31">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A22" s="28">
         <v>2080130200000</v>
       </c>
       <c r="B22" s="3">
@@ -2989,8 +2990,8 @@
         <v>6</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="15.75">
-      <c r="A23" s="31">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A23" s="28">
         <v>2080130200000</v>
       </c>
       <c r="B23" s="3">
@@ -3006,8 +3007,8 @@
         <v>6</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="15.75">
-      <c r="A24" s="31">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A24" s="28">
         <v>2080130200000</v>
       </c>
       <c r="B24" s="3">
@@ -3023,8 +3024,8 @@
         <v>6</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="15.75">
-      <c r="A25" s="31">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A25" s="28">
         <v>2080130200000</v>
       </c>
       <c r="B25" s="3">
@@ -3040,8 +3041,8 @@
         <v>6</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="15.75">
-      <c r="A26" s="31">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A26" s="28">
         <v>2080130200000</v>
       </c>
       <c r="B26" s="3">
@@ -3057,8 +3058,8 @@
         <v>6</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="15.75">
-      <c r="A27" s="31">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A27" s="28">
         <v>2080130200000</v>
       </c>
       <c r="B27" s="3">
@@ -3074,8 +3075,8 @@
         <v>6</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="15.75">
-      <c r="A28" s="31">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A28" s="28">
         <v>2080130200000</v>
       </c>
       <c r="B28" s="3">
@@ -3091,8 +3092,8 @@
         <v>6</v>
       </c>
     </row>
-    <row r="29" spans="1:7" ht="15.75">
-      <c r="A29" s="31">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A29" s="28">
         <v>2080130200000</v>
       </c>
       <c r="B29" s="3">
@@ -3108,8 +3109,8 @@
         <v>6</v>
       </c>
     </row>
-    <row r="30" spans="1:7" ht="15.75">
-      <c r="A30" s="31">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A30" s="28">
         <v>2080130200000</v>
       </c>
       <c r="B30" s="3">
@@ -3125,8 +3126,8 @@
         <v>6</v>
       </c>
     </row>
-    <row r="31" spans="1:7" ht="15.75">
-      <c r="A31" s="31">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A31" s="28">
         <v>2080130200000</v>
       </c>
       <c r="B31" s="3">
@@ -3142,8 +3143,8 @@
         <v>6</v>
       </c>
     </row>
-    <row r="32" spans="1:7" ht="15.75">
-      <c r="A32" s="31">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A32" s="28">
         <v>2080130200000</v>
       </c>
       <c r="B32" s="3">
@@ -3159,8 +3160,8 @@
         <v>6</v>
       </c>
     </row>
-    <row r="33" spans="1:7" ht="15.75">
-      <c r="A33" s="31">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A33" s="28">
         <v>2080130200000</v>
       </c>
       <c r="B33" s="3">
@@ -3176,8 +3177,8 @@
         <v>6</v>
       </c>
     </row>
-    <row r="34" spans="1:7" ht="15.75">
-      <c r="A34" s="31">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A34" s="28">
         <v>2080130200000</v>
       </c>
       <c r="B34" s="3">
@@ -3193,8 +3194,8 @@
         <v>6</v>
       </c>
     </row>
-    <row r="35" spans="1:7" ht="15.75">
-      <c r="A35" s="31">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A35" s="28">
         <v>2080130200000</v>
       </c>
       <c r="B35" s="3">
@@ -3210,59 +3211,59 @@
         <v>6</v>
       </c>
     </row>
-    <row r="36" spans="1:7" ht="15.75">
-      <c r="A36" s="35">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A36" s="32">
         <v>2080130200001</v>
       </c>
-      <c r="B36" s="36">
+      <c r="B36" s="33">
         <v>1974254</v>
       </c>
-      <c r="C36" s="36">
+      <c r="C36" s="33">
         <v>1974261</v>
       </c>
-      <c r="D36" s="36" t="s">
+      <c r="D36" s="33" t="s">
         <v>51</v>
       </c>
       <c r="G36" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="37" spans="1:7" ht="15.75">
-      <c r="A37" s="35">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A37" s="32">
         <v>2080130218001</v>
       </c>
-      <c r="B37" s="36">
+      <c r="B37" s="33">
         <v>1180166</v>
       </c>
-      <c r="C37" s="36">
+      <c r="C37" s="33">
         <v>1180166</v>
       </c>
-      <c r="D37" s="36" t="s">
+      <c r="D37" s="33" t="s">
         <v>52</v>
       </c>
       <c r="G37" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="38" spans="1:7" ht="15.75">
-      <c r="A38" s="35">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A38" s="32">
         <v>2080130218001</v>
       </c>
-      <c r="B38" s="36">
+      <c r="B38" s="33">
         <v>1180169</v>
       </c>
-      <c r="C38" s="36">
+      <c r="C38" s="33">
         <v>1180169</v>
       </c>
-      <c r="D38" s="36" t="s">
+      <c r="D38" s="33" t="s">
         <v>52</v>
       </c>
       <c r="G38" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="39" spans="1:7" ht="15.75">
-      <c r="A39" s="26">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A39" s="23">
         <v>2080150200000</v>
       </c>
       <c r="B39" s="3">
@@ -3271,15 +3272,15 @@
       <c r="C39" s="3">
         <v>2011805</v>
       </c>
-      <c r="D39" s="19" t="s">
+      <c r="D39" s="16" t="s">
         <v>51</v>
       </c>
       <c r="G39" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="40" spans="1:7" ht="15.75">
-      <c r="A40" s="26">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A40" s="23">
         <v>2080150200000</v>
       </c>
       <c r="B40" s="3">
@@ -3288,15 +3289,15 @@
       <c r="C40" s="3">
         <v>1974875</v>
       </c>
-      <c r="D40" s="13" t="s">
+      <c r="D40" s="10" t="s">
         <v>51</v>
       </c>
       <c r="G40" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="41" spans="1:7" ht="15.75">
-      <c r="A41" s="26">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A41" s="23">
         <v>2080150200000</v>
       </c>
       <c r="B41" s="3">
@@ -3305,15 +3306,15 @@
       <c r="C41" s="3">
         <v>2011761</v>
       </c>
-      <c r="D41" s="13" t="s">
+      <c r="D41" s="10" t="s">
         <v>51</v>
       </c>
       <c r="G41" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="42" spans="1:7" ht="15.75">
-      <c r="A42" s="26">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A42" s="23">
         <v>2080150200000</v>
       </c>
       <c r="B42" s="3">
@@ -3322,15 +3323,15 @@
       <c r="C42" s="3">
         <v>2014195</v>
       </c>
-      <c r="D42" s="13" t="s">
+      <c r="D42" s="10" t="s">
         <v>51</v>
       </c>
       <c r="G42" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="43" spans="1:7" ht="15.75">
-      <c r="A43" s="26">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A43" s="23">
         <v>2080150200000</v>
       </c>
       <c r="B43" s="3">
@@ -3339,15 +3340,15 @@
       <c r="C43" s="3">
         <v>2014075</v>
       </c>
-      <c r="D43" s="13" t="s">
+      <c r="D43" s="10" t="s">
         <v>51</v>
       </c>
       <c r="G43" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="44" spans="1:7" ht="15.75">
-      <c r="A44" s="26">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A44" s="23">
         <v>2080150200000</v>
       </c>
       <c r="B44" s="3">
@@ -3356,15 +3357,15 @@
       <c r="C44" s="3">
         <v>2014135</v>
       </c>
-      <c r="D44" s="13" t="s">
+      <c r="D44" s="10" t="s">
         <v>51</v>
       </c>
       <c r="G44" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="45" spans="1:7" ht="15.75">
-      <c r="A45" s="26">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A45" s="23">
         <v>2080150200000</v>
       </c>
       <c r="B45" s="3">
@@ -3373,15 +3374,15 @@
       <c r="C45" s="3">
         <v>2013955</v>
       </c>
-      <c r="D45" s="13" t="s">
+      <c r="D45" s="10" t="s">
         <v>51</v>
       </c>
       <c r="G45" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="46" spans="1:7" ht="15.75">
-      <c r="A46" s="26">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A46" s="23">
         <v>2080150200000</v>
       </c>
       <c r="B46" s="3">
@@ -3390,15 +3391,15 @@
       <c r="C46" s="3">
         <v>2014015</v>
       </c>
-      <c r="D46" s="13" t="s">
+      <c r="D46" s="10" t="s">
         <v>51</v>
       </c>
       <c r="G46" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="47" spans="1:7" ht="15.75">
-      <c r="A47" s="26">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A47" s="23">
         <v>2080150200000</v>
       </c>
       <c r="B47" s="3">
@@ -3407,15 +3408,15 @@
       <c r="C47" s="3">
         <v>2013835</v>
       </c>
-      <c r="D47" s="13" t="s">
+      <c r="D47" s="10" t="s">
         <v>51</v>
       </c>
       <c r="G47" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="48" spans="1:7" ht="15.75">
-      <c r="A48" s="26">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A48" s="23">
         <v>2080150200000</v>
       </c>
       <c r="B48" s="3">
@@ -3424,15 +3425,15 @@
       <c r="C48" s="3">
         <v>2013775</v>
       </c>
-      <c r="D48" s="13" t="s">
+      <c r="D48" s="10" t="s">
         <v>51</v>
       </c>
       <c r="G48" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="49" spans="1:7" ht="15.75">
-      <c r="A49" s="26">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A49" s="23">
         <v>2080150200000</v>
       </c>
       <c r="B49" s="3">
@@ -3441,15 +3442,15 @@
       <c r="C49" s="3">
         <v>2013895</v>
       </c>
-      <c r="D49" s="13" t="s">
+      <c r="D49" s="10" t="s">
         <v>51</v>
       </c>
       <c r="G49" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="50" spans="1:7" ht="15.95">
-      <c r="A50" s="26">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A50" s="23">
         <v>2080160400000</v>
       </c>
       <c r="B50" s="3">
@@ -3465,8 +3466,8 @@
         <v>6</v>
       </c>
     </row>
-    <row r="51" spans="1:7" ht="15.95">
-      <c r="A51" s="26">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A51" s="23">
         <v>2080160400000</v>
       </c>
       <c r="B51" s="3">
@@ -3482,8 +3483,8 @@
         <v>6</v>
       </c>
     </row>
-    <row r="52" spans="1:7" ht="15.95">
-      <c r="A52" s="26">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A52" s="23">
         <v>2080160400000</v>
       </c>
       <c r="B52" s="3">
@@ -3499,8 +3500,8 @@
         <v>6</v>
       </c>
     </row>
-    <row r="53" spans="1:7" ht="15.95">
-      <c r="A53" s="26">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A53" s="23">
         <v>2080160400000</v>
       </c>
       <c r="B53" s="3">
@@ -3516,8 +3517,8 @@
         <v>6</v>
       </c>
     </row>
-    <row r="54" spans="1:7" ht="15.95">
-      <c r="A54" s="26">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A54" s="23">
         <v>2080160400000</v>
       </c>
       <c r="B54" s="3">
@@ -3533,8 +3534,8 @@
         <v>6</v>
       </c>
     </row>
-    <row r="55" spans="1:7" ht="15.95">
-      <c r="A55" s="26">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A55" s="23">
         <v>2080160400000</v>
       </c>
       <c r="B55" s="3">
@@ -3550,8 +3551,8 @@
         <v>6</v>
       </c>
     </row>
-    <row r="56" spans="1:7" ht="15.95">
-      <c r="A56" s="26">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A56" s="23">
         <v>2080160400000</v>
       </c>
       <c r="B56" s="3">
@@ -3567,8 +3568,8 @@
         <v>6</v>
       </c>
     </row>
-    <row r="57" spans="1:7" ht="15.95">
-      <c r="A57" s="26">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A57" s="23">
         <v>2080160400000</v>
       </c>
       <c r="B57" s="3">
@@ -3584,8 +3585,8 @@
         <v>6</v>
       </c>
     </row>
-    <row r="58" spans="1:7" ht="15.95">
-      <c r="A58" s="26">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A58" s="23">
         <v>2080160400000</v>
       </c>
       <c r="B58" s="3">
@@ -3601,8 +3602,8 @@
         <v>6</v>
       </c>
     </row>
-    <row r="59" spans="1:7" ht="15.95">
-      <c r="A59" s="26">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A59" s="23">
         <v>2080160400000</v>
       </c>
       <c r="B59" s="3">
@@ -3618,8 +3619,8 @@
         <v>6</v>
       </c>
     </row>
-    <row r="60" spans="1:7" ht="15.95">
-      <c r="A60" s="26">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A60" s="23">
         <v>2080160400000</v>
       </c>
       <c r="B60" s="3">
@@ -3635,8 +3636,8 @@
         <v>6</v>
       </c>
     </row>
-    <row r="61" spans="1:7" ht="15.95">
-      <c r="A61" s="26">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A61" s="23">
         <v>2080160400000</v>
       </c>
       <c r="B61" s="3">
@@ -3652,42 +3653,42 @@
         <v>6</v>
       </c>
     </row>
-    <row r="62" spans="1:7" ht="15.95">
-      <c r="A62" s="37">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A62" s="34">
         <v>2080160400001</v>
       </c>
-      <c r="B62" s="38">
+      <c r="B62" s="35">
         <v>1927218</v>
       </c>
-      <c r="C62" s="38">
+      <c r="C62" s="35">
         <v>1927218</v>
       </c>
-      <c r="D62" s="38" t="s">
+      <c r="D62" s="35" t="s">
         <v>52</v>
       </c>
       <c r="G62" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="63" spans="1:7" ht="15.95">
-      <c r="A63" s="37">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A63" s="34">
         <v>2080160400001</v>
       </c>
-      <c r="B63" s="38">
+      <c r="B63" s="35">
         <v>1927220</v>
       </c>
-      <c r="C63" s="38">
+      <c r="C63" s="35">
         <v>1927221</v>
       </c>
-      <c r="D63" s="38" t="s">
+      <c r="D63" s="35" t="s">
         <v>52</v>
       </c>
       <c r="G63" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="64" spans="1:7" ht="15.95">
-      <c r="A64" s="26">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A64" s="23">
         <v>2080060000000</v>
       </c>
       <c r="B64" s="3">
@@ -3703,8 +3704,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="65" spans="1:7" ht="15.95">
-      <c r="A65" s="26">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A65" s="23">
         <v>2080060000001</v>
       </c>
       <c r="B65" s="3">
@@ -3720,8 +3721,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="66" spans="1:7" ht="15.95">
-      <c r="A66" s="26">
+    <row r="66" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A66" s="23">
         <v>2080060000001</v>
       </c>
       <c r="B66" s="3">
@@ -3737,8 +3738,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="67" spans="1:7" ht="15.95">
-      <c r="A67" s="26">
+    <row r="67" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A67" s="23">
         <v>2080070000000</v>
       </c>
       <c r="B67" s="3">
@@ -3754,8 +3755,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="68" spans="1:7" ht="15.95">
-      <c r="A68" s="39">
+    <row r="68" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A68" s="36">
         <v>20801702</v>
       </c>
       <c r="B68" s="3">
@@ -3771,8 +3772,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="69" spans="1:7" ht="15.95">
-      <c r="A69" s="40">
+    <row r="69" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A69" s="37">
         <v>2080924700000</v>
       </c>
       <c r="B69" s="3">
@@ -3788,8 +3789,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="70" spans="1:7" ht="15.95">
-      <c r="A70" s="40">
+    <row r="70" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A70" s="37">
         <v>2080924700000</v>
       </c>
       <c r="B70" s="3">
@@ -3805,8 +3806,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="71" spans="1:7" ht="15.95">
-      <c r="A71" s="40">
+    <row r="71" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A71" s="37">
         <v>2080924700000</v>
       </c>
       <c r="B71" s="3">
@@ -3822,8 +3823,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="72" spans="1:7" ht="15.95">
-      <c r="A72" s="40">
+    <row r="72" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A72" s="37">
         <v>2080924700000</v>
       </c>
       <c r="B72" s="3">
@@ -3839,8 +3840,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="73" spans="1:7" ht="15.95">
-      <c r="A73" s="40">
+    <row r="73" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A73" s="37">
         <v>2080924700000</v>
       </c>
       <c r="B73" s="3">
@@ -3856,8 +3857,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="74" spans="1:7" ht="15.95">
-      <c r="A74" s="40">
+    <row r="74" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A74" s="37">
         <v>2080924700000</v>
       </c>
       <c r="B74" s="3">
@@ -3873,8 +3874,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="75" spans="1:7" ht="15.95">
-      <c r="A75" s="40">
+    <row r="75" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A75" s="37">
         <v>2080924700000</v>
       </c>
       <c r="B75" s="3">
@@ -3890,8 +3891,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="76" spans="1:7" ht="15.95">
-      <c r="A76" s="40">
+    <row r="76" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A76" s="37">
         <v>2080924700000</v>
       </c>
       <c r="B76" s="3">
@@ -3907,8 +3908,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="77" spans="1:7" ht="15.95">
-      <c r="A77" s="40">
+    <row r="77" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A77" s="37">
         <v>2080924700000</v>
       </c>
       <c r="B77" s="3">
@@ -3924,8 +3925,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="78" spans="1:7" ht="15.95">
-      <c r="A78" s="40">
+    <row r="78" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A78" s="37">
         <v>2080924700000</v>
       </c>
       <c r="B78" s="3">
@@ -3941,8 +3942,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="79" spans="1:7" ht="15.95">
-      <c r="A79" s="40">
+    <row r="79" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A79" s="37">
         <v>2080924700000</v>
       </c>
       <c r="B79" s="3">
@@ -3958,8 +3959,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="80" spans="1:7" ht="15.95">
-      <c r="A80" s="40">
+    <row r="80" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A80" s="37">
         <v>2080924700000</v>
       </c>
       <c r="B80" s="3">
@@ -3975,8 +3976,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="81" spans="1:7" ht="15.95">
-      <c r="A81" s="40">
+    <row r="81" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A81" s="37">
         <v>2080924700000</v>
       </c>
       <c r="B81" s="3">
@@ -3992,8 +3993,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="82" spans="1:7" ht="15.95">
-      <c r="A82" s="40">
+    <row r="82" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A82" s="37">
         <v>2080924700000</v>
       </c>
       <c r="B82" s="3">
@@ -4009,8 +4010,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="83" spans="1:7" ht="15.95">
-      <c r="A83" s="40">
+    <row r="83" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A83" s="37">
         <v>2080924700000</v>
       </c>
       <c r="B83" s="3">
@@ -4026,8 +4027,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="84" spans="1:7" ht="15.95">
-      <c r="A84" s="40">
+    <row r="84" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A84" s="37">
         <v>2080924700000</v>
       </c>
       <c r="B84" s="3">
@@ -4043,8 +4044,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="85" spans="1:7" ht="15.95">
-      <c r="A85" s="40">
+    <row r="85" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A85" s="37">
         <v>2080430000000</v>
       </c>
       <c r="B85" s="3">
@@ -4060,8 +4061,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="86" spans="1:7" ht="15.75">
-      <c r="A86" s="41">
+    <row r="86" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A86" s="38">
         <v>2080010000000</v>
       </c>
       <c r="B86" s="3">
@@ -4070,15 +4071,15 @@
       <c r="C86" s="3">
         <v>1721479</v>
       </c>
-      <c r="D86" s="19" t="s">
+      <c r="D86" s="16" t="s">
         <v>57</v>
       </c>
       <c r="G86" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="87" spans="1:7" ht="15.75">
-      <c r="A87" s="41">
+    <row r="87" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A87" s="38">
         <v>2080010000000</v>
       </c>
       <c r="B87" s="3">
@@ -4087,15 +4088,15 @@
       <c r="C87" s="3">
         <v>1721464</v>
       </c>
-      <c r="D87" s="13" t="s">
+      <c r="D87" s="10" t="s">
         <v>57</v>
       </c>
       <c r="G87" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="88" spans="1:7" ht="15.75">
-      <c r="A88" s="40">
+    <row r="88" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A88" s="37">
         <v>2080030400000</v>
       </c>
       <c r="B88" s="3">
@@ -4104,15 +4105,15 @@
       <c r="C88" s="3">
         <v>1721442</v>
       </c>
-      <c r="D88" s="13" t="s">
+      <c r="D88" s="10" t="s">
         <v>57</v>
       </c>
       <c r="G88" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="89" spans="1:7" ht="15.75">
-      <c r="A89" s="40">
+    <row r="89" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A89" s="37">
         <v>2080030400000</v>
       </c>
       <c r="B89" s="3">
@@ -4121,15 +4122,15 @@
       <c r="C89" s="3">
         <v>1721451</v>
       </c>
-      <c r="D89" s="13" t="s">
+      <c r="D89" s="10" t="s">
         <v>57</v>
       </c>
       <c r="G89" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="90" spans="1:7" ht="15.75">
-      <c r="A90" s="40">
+    <row r="90" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A90" s="37">
         <v>2080030400000</v>
       </c>
       <c r="B90" s="3">
@@ -4138,15 +4139,15 @@
       <c r="C90" s="3">
         <v>1721441</v>
       </c>
-      <c r="D90" s="13" t="s">
+      <c r="D90" s="10" t="s">
         <v>57</v>
       </c>
       <c r="G90" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="91" spans="1:7" ht="15.75">
-      <c r="A91" s="40">
+    <row r="91" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A91" s="37">
         <v>2080030400000</v>
       </c>
       <c r="B91" s="3">
@@ -4155,15 +4156,15 @@
       <c r="C91" s="3">
         <v>1721431</v>
       </c>
-      <c r="D91" s="13" t="s">
+      <c r="D91" s="10" t="s">
         <v>57</v>
       </c>
       <c r="G91" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="92" spans="1:7" ht="15.75">
-      <c r="A92" s="40">
+    <row r="92" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A92" s="37">
         <v>2080030400000</v>
       </c>
       <c r="B92" s="3">
@@ -4172,15 +4173,15 @@
       <c r="C92" s="3">
         <v>1721386</v>
       </c>
-      <c r="D92" s="13" t="s">
+      <c r="D92" s="10" t="s">
         <v>57</v>
       </c>
       <c r="G92" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="93" spans="1:7" ht="15.75">
-      <c r="A93" s="40">
+    <row r="93" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A93" s="37">
         <v>2080020400000</v>
       </c>
       <c r="B93" s="3">
@@ -4189,15 +4190,15 @@
       <c r="C93" s="3">
         <v>172422</v>
       </c>
-      <c r="D93" s="13" t="s">
+      <c r="D93" s="10" t="s">
         <v>57</v>
       </c>
       <c r="G93" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="94" spans="1:7" ht="15.75">
-      <c r="A94" s="40">
+    <row r="94" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A94" s="37">
         <v>2080020400000</v>
       </c>
       <c r="B94" s="3">
@@ -4206,15 +4207,15 @@
       <c r="C94" s="3">
         <v>1721324</v>
       </c>
-      <c r="D94" s="13" t="s">
+      <c r="D94" s="10" t="s">
         <v>57</v>
       </c>
       <c r="G94" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="95" spans="1:7" ht="15.75">
-      <c r="A95" s="40">
+    <row r="95" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A95" s="37">
         <v>2080020400000</v>
       </c>
       <c r="B95" s="3">
@@ -4223,15 +4224,15 @@
       <c r="C95" s="3">
         <v>1721313</v>
       </c>
-      <c r="D95" s="13" t="s">
+      <c r="D95" s="10" t="s">
         <v>57</v>
       </c>
       <c r="G95" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="96" spans="1:7" ht="15.75">
-      <c r="A96" s="40">
+    <row r="96" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A96" s="37">
         <v>2080020400000</v>
       </c>
       <c r="B96" s="3">
@@ -4240,15 +4241,15 @@
       <c r="C96" s="3">
         <v>1721315</v>
       </c>
-      <c r="D96" s="13" t="s">
+      <c r="D96" s="10" t="s">
         <v>57</v>
       </c>
       <c r="G96" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="97" spans="1:7" ht="15.75">
-      <c r="A97" s="40">
+    <row r="97" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A97" s="37">
         <v>2080020400000</v>
       </c>
       <c r="B97" s="3">
@@ -4257,15 +4258,15 @@
       <c r="C97" s="3">
         <v>1721416</v>
       </c>
-      <c r="D97" s="13" t="s">
+      <c r="D97" s="10" t="s">
         <v>57</v>
       </c>
       <c r="G97" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="98" spans="1:7" ht="15.75">
-      <c r="A98" s="40">
+    <row r="98" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A98" s="37">
         <v>2080020400000</v>
       </c>
       <c r="B98" s="3">
@@ -4274,15 +4275,15 @@
       <c r="C98" s="3">
         <v>1721404</v>
       </c>
-      <c r="D98" s="13" t="s">
+      <c r="D98" s="10" t="s">
         <v>57</v>
       </c>
       <c r="G98" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="99" spans="1:7" ht="15.95">
-      <c r="A99" s="42">
+    <row r="99" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A99" s="39">
         <v>2080021100000</v>
       </c>
       <c r="B99" s="4">
@@ -4298,8 +4299,8 @@
         <v>13</v>
       </c>
     </row>
-    <row r="100" spans="1:7" ht="15.95">
-      <c r="A100" s="42">
+    <row r="100" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A100" s="39">
         <v>2080021100000</v>
       </c>
       <c r="B100" s="4">
@@ -4315,8 +4316,8 @@
         <v>13</v>
       </c>
     </row>
-    <row r="101" spans="1:7" ht="15.95">
-      <c r="A101" s="42">
+    <row r="101" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A101" s="39">
         <v>2080021100000</v>
       </c>
       <c r="B101" s="4">
@@ -4332,8 +4333,8 @@
         <v>13</v>
       </c>
     </row>
-    <row r="102" spans="1:7" ht="15.95">
-      <c r="A102" s="42">
+    <row r="102" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A102" s="39">
         <v>2080021200000</v>
       </c>
       <c r="B102" s="4">
@@ -4349,8 +4350,8 @@
         <v>13</v>
       </c>
     </row>
-    <row r="103" spans="1:7" ht="15.95">
-      <c r="A103" s="9">
+    <row r="103" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A103" s="6">
         <v>2080926000000</v>
       </c>
       <c r="B103" s="3">
@@ -4366,8 +4367,8 @@
         <v>62</v>
       </c>
     </row>
-    <row r="104" spans="1:7" ht="15.95">
-      <c r="A104" s="9">
+    <row r="104" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A104" s="6">
         <v>2080926000000</v>
       </c>
       <c r="B104" s="3">
@@ -4383,8 +4384,8 @@
         <v>62</v>
       </c>
     </row>
-    <row r="105" spans="1:7" ht="15.95">
-      <c r="A105" s="9">
+    <row r="105" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A105" s="6">
         <v>2080926300000</v>
       </c>
       <c r="B105" s="3">
@@ -4400,8 +4401,8 @@
         <v>62</v>
       </c>
     </row>
-    <row r="106" spans="1:7" ht="15.95">
-      <c r="A106" s="9">
+    <row r="106" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A106" s="6">
         <v>2080926300000</v>
       </c>
       <c r="B106" s="3">
@@ -4417,59 +4418,59 @@
         <v>62</v>
       </c>
     </row>
-    <row r="107" spans="1:7" ht="15.95">
-      <c r="A107" s="9">
+    <row r="107" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A107" s="6">
         <v>2080926300000</v>
       </c>
-      <c r="B107" s="27" t="s">
+      <c r="B107" s="24" t="s">
         <v>58</v>
       </c>
-      <c r="C107" s="27" t="s">
+      <c r="C107" s="24" t="s">
         <v>58</v>
       </c>
-      <c r="D107" s="28" t="s">
+      <c r="D107" s="25" t="s">
         <v>61</v>
       </c>
       <c r="G107" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="108" spans="1:7" ht="15.95">
-      <c r="A108" s="9">
+    <row r="108" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A108" s="6">
         <v>2080926300000</v>
       </c>
-      <c r="B108" s="27" t="s">
+      <c r="B108" s="24" t="s">
         <v>59</v>
       </c>
-      <c r="C108" s="27" t="s">
+      <c r="C108" s="24" t="s">
         <v>59</v>
       </c>
-      <c r="D108" s="28" t="s">
+      <c r="D108" s="25" t="s">
         <v>61</v>
       </c>
       <c r="G108" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="109" spans="1:7" ht="15.95">
-      <c r="A109" s="9">
+    <row r="109" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A109" s="6">
         <v>2080926300000</v>
       </c>
-      <c r="B109" s="27" t="s">
+      <c r="B109" s="24" t="s">
         <v>60</v>
       </c>
-      <c r="C109" s="27" t="s">
+      <c r="C109" s="24" t="s">
         <v>60</v>
       </c>
-      <c r="D109" s="28" t="s">
+      <c r="D109" s="25" t="s">
         <v>61</v>
       </c>
       <c r="G109" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="110" spans="1:7" ht="15.95">
-      <c r="A110" s="43">
+    <row r="110" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A110" s="40">
         <v>2080927200000</v>
       </c>
       <c r="B110" s="4">
@@ -4485,8 +4486,8 @@
         <v>63</v>
       </c>
     </row>
-    <row r="111" spans="1:7" ht="15.95">
-      <c r="A111" s="44">
+    <row r="111" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A111" s="41">
         <v>8080009918001</v>
       </c>
       <c r="B111" s="3">
@@ -4502,8 +4503,8 @@
         <v>14</v>
       </c>
     </row>
-    <row r="112" spans="1:7" ht="15.95">
-      <c r="A112" s="45">
+    <row r="112" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A112" s="42">
         <v>8080009918001</v>
       </c>
       <c r="B112" s="3">
@@ -4519,8 +4520,8 @@
         <v>14</v>
       </c>
     </row>
-    <row r="113" spans="1:7" ht="15.95">
-      <c r="A113" s="45">
+    <row r="113" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A113" s="42">
         <v>8080009918001</v>
       </c>
       <c r="B113" s="3">
@@ -4536,8 +4537,8 @@
         <v>14</v>
       </c>
     </row>
-    <row r="114" spans="1:7" ht="15.95">
-      <c r="A114" s="45">
+    <row r="114" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A114" s="42">
         <v>8080009918001</v>
       </c>
       <c r="B114" s="3">
@@ -4553,8 +4554,8 @@
         <v>14</v>
       </c>
     </row>
-    <row r="115" spans="1:7" ht="15.95">
-      <c r="A115" s="45">
+    <row r="115" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A115" s="42">
         <v>8080009918001</v>
       </c>
       <c r="B115" s="3">
@@ -4570,8 +4571,8 @@
         <v>14</v>
       </c>
     </row>
-    <row r="116" spans="1:7" ht="15.95">
-      <c r="A116" s="45">
+    <row r="116" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A116" s="42">
         <v>8080009918001</v>
       </c>
       <c r="B116" s="3">
@@ -4587,8 +4588,8 @@
         <v>14</v>
       </c>
     </row>
-    <row r="117" spans="1:7" ht="15.95">
-      <c r="A117" s="45">
+    <row r="117" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A117" s="42">
         <v>8080009918001</v>
       </c>
       <c r="B117" s="3">
@@ -4604,8 +4605,8 @@
         <v>14</v>
       </c>
     </row>
-    <row r="118" spans="1:7" ht="15.95">
-      <c r="A118" s="45">
+    <row r="118" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A118" s="42">
         <v>8080009918001</v>
       </c>
       <c r="B118" s="3">
@@ -4621,8 +4622,8 @@
         <v>14</v>
       </c>
     </row>
-    <row r="119" spans="1:7" ht="15.95">
-      <c r="A119" s="45">
+    <row r="119" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A119" s="42">
         <v>8080009918001</v>
       </c>
       <c r="B119" s="3">
@@ -4638,8 +4639,8 @@
         <v>14</v>
       </c>
     </row>
-    <row r="120" spans="1:7" ht="15.95">
-      <c r="A120" s="45">
+    <row r="120" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A120" s="42">
         <v>8080009918001</v>
       </c>
       <c r="B120" s="3">
@@ -4655,8 +4656,8 @@
         <v>14</v>
       </c>
     </row>
-    <row r="121" spans="1:7" ht="15.95">
-      <c r="A121" s="45">
+    <row r="121" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A121" s="42">
         <v>8080009918001</v>
       </c>
       <c r="B121" s="3">
@@ -4672,8 +4673,8 @@
         <v>14</v>
       </c>
     </row>
-    <row r="122" spans="1:7" ht="15.95">
-      <c r="A122" s="45">
+    <row r="122" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A122" s="42">
         <v>8080009918001</v>
       </c>
       <c r="B122" s="3">
@@ -4689,8 +4690,8 @@
         <v>14</v>
       </c>
     </row>
-    <row r="123" spans="1:7" ht="15.95">
-      <c r="A123" s="45">
+    <row r="123" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A123" s="42">
         <v>8080009918001</v>
       </c>
       <c r="B123" s="3">
@@ -4706,8 +4707,8 @@
         <v>14</v>
       </c>
     </row>
-    <row r="124" spans="1:7" ht="15.95">
-      <c r="A124" s="45">
+    <row r="124" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A124" s="42">
         <v>8080009918001</v>
       </c>
       <c r="B124" s="3">
@@ -4723,8 +4724,8 @@
         <v>14</v>
       </c>
     </row>
-    <row r="125" spans="1:7" ht="15.95">
-      <c r="A125" s="45">
+    <row r="125" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A125" s="42">
         <v>8080009918001</v>
       </c>
       <c r="B125" s="3">
@@ -4740,8 +4741,8 @@
         <v>14</v>
       </c>
     </row>
-    <row r="126" spans="1:7" ht="15.95">
-      <c r="A126" s="45">
+    <row r="126" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A126" s="42">
         <v>8080009918001</v>
       </c>
       <c r="B126" s="3">
@@ -4757,8 +4758,8 @@
         <v>14</v>
       </c>
     </row>
-    <row r="127" spans="1:7" ht="15.95">
-      <c r="A127" s="45">
+    <row r="127" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A127" s="42">
         <v>8080009918001</v>
       </c>
       <c r="B127" s="3">
@@ -4774,8 +4775,8 @@
         <v>14</v>
       </c>
     </row>
-    <row r="128" spans="1:7" ht="15.95">
-      <c r="A128" s="45">
+    <row r="128" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A128" s="42">
         <v>8080009918001</v>
       </c>
       <c r="B128" s="3">
@@ -4791,8 +4792,8 @@
         <v>14</v>
       </c>
     </row>
-    <row r="129" spans="1:7" ht="15.95">
-      <c r="A129" s="45">
+    <row r="129" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A129" s="42">
         <v>8080009918001</v>
       </c>
       <c r="B129" s="3">
@@ -4808,8 +4809,8 @@
         <v>14</v>
       </c>
     </row>
-    <row r="130" spans="1:7" ht="15.95">
-      <c r="A130" s="45">
+    <row r="130" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A130" s="42">
         <v>8080009918001</v>
       </c>
       <c r="B130" s="3">
@@ -4825,8 +4826,8 @@
         <v>14</v>
       </c>
     </row>
-    <row r="131" spans="1:7" ht="15.95">
-      <c r="A131" s="45">
+    <row r="131" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A131" s="42">
         <v>8080009918001</v>
       </c>
       <c r="B131" s="3">
@@ -4842,8 +4843,8 @@
         <v>14</v>
       </c>
     </row>
-    <row r="132" spans="1:7" ht="15.95">
-      <c r="A132" s="45">
+    <row r="132" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A132" s="42">
         <v>8080009918001</v>
       </c>
       <c r="B132" s="3">
@@ -4859,8 +4860,8 @@
         <v>14</v>
       </c>
     </row>
-    <row r="133" spans="1:7" ht="15.95">
-      <c r="A133" s="45">
+    <row r="133" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A133" s="42">
         <v>8080009918001</v>
       </c>
       <c r="B133" s="3">
@@ -4876,8 +4877,8 @@
         <v>14</v>
       </c>
     </row>
-    <row r="134" spans="1:7" ht="15.95">
-      <c r="A134" s="45">
+    <row r="134" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A134" s="42">
         <v>8080009918001</v>
       </c>
       <c r="B134" s="3">
@@ -4893,8 +4894,8 @@
         <v>14</v>
       </c>
     </row>
-    <row r="135" spans="1:7" ht="15.95">
-      <c r="A135" s="45">
+    <row r="135" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A135" s="42">
         <v>8080009918001</v>
       </c>
       <c r="B135" s="3">
@@ -4910,8 +4911,8 @@
         <v>14</v>
       </c>
     </row>
-    <row r="136" spans="1:7" ht="15.95">
-      <c r="A136" s="45">
+    <row r="136" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A136" s="42">
         <v>8080009918001</v>
       </c>
       <c r="B136" s="3">
@@ -4927,8 +4928,8 @@
         <v>14</v>
       </c>
     </row>
-    <row r="137" spans="1:7" ht="15.95">
-      <c r="A137" s="45">
+    <row r="137" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A137" s="42">
         <v>8080009918001</v>
       </c>
       <c r="B137" s="3">
@@ -4944,8 +4945,8 @@
         <v>14</v>
       </c>
     </row>
-    <row r="138" spans="1:7" ht="15.95">
-      <c r="A138" s="45">
+    <row r="138" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A138" s="42">
         <v>8080009918001</v>
       </c>
       <c r="B138" s="3">
@@ -4961,8 +4962,8 @@
         <v>14</v>
       </c>
     </row>
-    <row r="139" spans="1:7" ht="15.95">
-      <c r="A139" s="45">
+    <row r="139" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A139" s="42">
         <v>8080009918001</v>
       </c>
       <c r="B139" s="3">
@@ -4978,8 +4979,8 @@
         <v>14</v>
       </c>
     </row>
-    <row r="140" spans="1:7" ht="15.75">
-      <c r="A140" s="46">
+    <row r="140" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A140" s="43">
         <v>9070010000000</v>
       </c>
       <c r="B140" s="3">
@@ -4988,15 +4989,15 @@
       <c r="C140" s="3">
         <v>135999</v>
       </c>
-      <c r="D140" s="48" t="s">
+      <c r="D140" s="45" t="s">
         <v>65</v>
       </c>
       <c r="G140" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="141" spans="1:7" ht="15.75">
-      <c r="A141" s="47">
+    <row r="141" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A141" s="44">
         <v>9070010000000</v>
       </c>
       <c r="B141" s="3">
@@ -5005,15 +5006,15 @@
       <c r="C141" s="3">
         <v>138459</v>
       </c>
-      <c r="D141" s="48" t="s">
+      <c r="D141" s="45" t="s">
         <v>65</v>
       </c>
       <c r="G141" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="142" spans="1:7" ht="15.75">
-      <c r="A142" s="47">
+    <row r="142" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A142" s="44">
         <v>9070010000000</v>
       </c>
       <c r="B142" s="3">
@@ -5022,15 +5023,15 @@
       <c r="C142" s="3">
         <v>138455</v>
       </c>
-      <c r="D142" s="48" t="s">
+      <c r="D142" s="45" t="s">
         <v>65</v>
       </c>
       <c r="G142" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="143" spans="1:7" ht="15.75">
-      <c r="A143" s="47">
+    <row r="143" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A143" s="44">
         <v>9070010000000</v>
       </c>
       <c r="B143" s="3">
@@ -5039,15 +5040,15 @@
       <c r="C143" s="3">
         <v>138473</v>
       </c>
-      <c r="D143" s="48" t="s">
+      <c r="D143" s="45" t="s">
         <v>65</v>
       </c>
       <c r="G143" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="144" spans="1:7" ht="15.75">
-      <c r="A144" s="47">
+    <row r="144" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A144" s="44">
         <v>9070010000000</v>
       </c>
       <c r="B144" s="3">
@@ -5056,15 +5057,15 @@
       <c r="C144" s="3">
         <v>138469</v>
       </c>
-      <c r="D144" s="48" t="s">
+      <c r="D144" s="45" t="s">
         <v>65</v>
       </c>
       <c r="G144" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="145" spans="1:7" ht="15.75">
-      <c r="A145" s="47">
+    <row r="145" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A145" s="44">
         <v>9070010000000</v>
       </c>
       <c r="B145" s="3">
@@ -5073,15 +5074,15 @@
       <c r="C145" s="3">
         <v>138456</v>
       </c>
-      <c r="D145" s="48" t="s">
+      <c r="D145" s="45" t="s">
         <v>65</v>
       </c>
       <c r="G145" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="146" spans="1:7" ht="15.75">
-      <c r="A146" s="47">
+    <row r="146" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A146" s="44">
         <v>9070010000000</v>
       </c>
       <c r="B146" s="3">
@@ -5097,8 +5098,8 @@
         <v>15</v>
       </c>
     </row>
-    <row r="147" spans="1:7" ht="15.75">
-      <c r="A147" s="47">
+    <row r="147" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A147" s="44">
         <v>9070010000000</v>
       </c>
       <c r="B147" s="3">
@@ -5114,8 +5115,8 @@
         <v>15</v>
       </c>
     </row>
-    <row r="148" spans="1:7" ht="15.75">
-      <c r="A148" s="47">
+    <row r="148" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A148" s="44">
         <v>9070010000000</v>
       </c>
       <c r="B148" s="3">
@@ -5131,8 +5132,8 @@
         <v>15</v>
       </c>
     </row>
-    <row r="149" spans="1:7" ht="15.75">
-      <c r="A149" s="47">
+    <row r="149" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A149" s="44">
         <v>9070010000000</v>
       </c>
       <c r="B149" s="3">
@@ -5148,8 +5149,8 @@
         <v>15</v>
       </c>
     </row>
-    <row r="150" spans="1:7" ht="15.75">
-      <c r="A150" s="47">
+    <row r="150" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A150" s="44">
         <v>9070010000000</v>
       </c>
       <c r="B150" s="3">
@@ -5165,8 +5166,8 @@
         <v>15</v>
       </c>
     </row>
-    <row r="151" spans="1:7" ht="15.75">
-      <c r="A151" s="47">
+    <row r="151" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A151" s="44">
         <v>9070010000000</v>
       </c>
       <c r="B151" s="3">
@@ -5182,8 +5183,8 @@
         <v>15</v>
       </c>
     </row>
-    <row r="152" spans="1:7" ht="15.75">
-      <c r="A152" s="47">
+    <row r="152" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A152" s="44">
         <v>9070010000000</v>
       </c>
       <c r="B152" s="3">
@@ -5199,8 +5200,8 @@
         <v>15</v>
       </c>
     </row>
-    <row r="153" spans="1:7" ht="15.75">
-      <c r="A153" s="47">
+    <row r="153" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A153" s="44">
         <v>9070010000000</v>
       </c>
       <c r="B153" s="3">
@@ -5216,8 +5217,8 @@
         <v>15</v>
       </c>
     </row>
-    <row r="154" spans="1:7" ht="15.75">
-      <c r="A154" s="47">
+    <row r="154" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A154" s="44">
         <v>9070010000000</v>
       </c>
       <c r="B154" s="3">
@@ -5233,8 +5234,8 @@
         <v>15</v>
       </c>
     </row>
-    <row r="155" spans="1:7" ht="15.75">
-      <c r="A155" s="47">
+    <row r="155" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A155" s="44">
         <v>9070010000000</v>
       </c>
       <c r="B155" s="3">
@@ -5250,8 +5251,8 @@
         <v>15</v>
       </c>
     </row>
-    <row r="156" spans="1:7" ht="15.75">
-      <c r="A156" s="46">
+    <row r="156" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A156" s="43">
         <v>9070010000000</v>
       </c>
       <c r="B156" s="3">
@@ -5260,7 +5261,7 @@
       <c r="C156" s="3">
         <v>138679</v>
       </c>
-      <c r="D156" s="28" t="s">
+      <c r="D156" s="25" t="s">
         <v>61</v>
       </c>
       <c r="G156" t="s">
